--- a/data/trans_dic/P32C-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32C-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca</t>
+          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,09</t>
+          <t>1,4; 3,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,46</t>
+          <t>0,91; 3,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,46</t>
+          <t>2,02; 6,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,46</t>
+          <t>1,82; 6,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,64</t>
+          <t>0,0; 6,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 4,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,68</t>
+          <t>1,32; 3,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,28</t>
+          <t>0,65; 2,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,62</t>
+          <t>1,69; 4,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,26</t>
+          <t>1,75; 4,99</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,67</t>
+          <t>0,99; 2,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,9</t>
+          <t>1,27; 2,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,99</t>
+          <t>0,69; 1,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,34</t>
+          <t>0,31; 1,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,72</t>
+          <t>0,19; 1,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,54</t>
+          <t>0,17; 1,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,35</t>
+          <t>0,15; 1,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,53</t>
+          <t>0,32; 2,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,01</t>
+          <t>0,81; 1,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,16</t>
+          <t>1,01; 2,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,5</t>
+          <t>0,6; 1,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,56</t>
+          <t>0,45; 1,47</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,83</t>
+          <t>0,81; 3,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,91</t>
+          <t>0,86; 5,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,62</t>
+          <t>0,28; 2,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,46</t>
+          <t>0,22; 2,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,86</t>
+          <t>0,67; 2,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,19</t>
+          <t>0,51; 3,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,66</t>
+          <t>0,28; 1,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,4</t>
+          <t>0,15; 1,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,65</t>
+          <t>1,34; 2,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,65</t>
+          <t>1,42; 2,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,29</t>
+          <t>1,13; 2,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,76</t>
+          <t>0,78; 1,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,83</t>
+          <t>0,39; 1,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,88</t>
+          <t>0,1; 0,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,19</t>
+          <t>0,19; 1,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,95</t>
+          <t>0,35; 1,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,15</t>
+          <t>1,14; 2,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,89</t>
+          <t>1,03; 1,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,7</t>
+          <t>0,86; 1,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,5</t>
+          <t>0,68; 1,52</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca</t>
+          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6446; 19272</t>
+          <t>6571; 18582</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4658; 17488</t>
+          <t>4596; 16885</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6848; 22708</t>
+          <t>7105; 21665</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4630; 15756</t>
+          <t>4442; 14753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 11117</t>
+          <t>0; 11058</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2059</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6006</t>
+          <t>0; 6176</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2606</t>
+          <t>0; 2935</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8157; 23495</t>
+          <t>8438; 23738</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4950; 16700</t>
+          <t>4754; 17646</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7456; 22556</t>
+          <t>8246; 24350</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5164; 16360</t>
+          <t>5432; 15523</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10047; 28274</t>
+          <t>10449; 29667</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14193; 34704</t>
+          <t>15246; 33909</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8496; 24744</t>
+          <t>8534; 24197</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3322; 13174</t>
+          <t>3033; 13363</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1010; 9178</t>
+          <t>1016; 10035</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1000; 9110</t>
+          <t>991; 8031</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1009; 9607</t>
+          <t>1087; 10525</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1985; 17930</t>
+          <t>2242; 17662</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13212; 32052</t>
+          <t>12883; 31376</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18080; 38604</t>
+          <t>17997; 37744</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11859; 29326</t>
+          <t>11700; 29816</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7826; 26416</t>
+          <t>7624; 24961</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2746; 13414</t>
+          <t>2846; 13913</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2102; 15915</t>
+          <t>2800; 17399</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1032; 9845</t>
+          <t>1055; 9874</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>863; 8478</t>
+          <t>746; 7611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5133</t>
+          <t>0; 5512</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2125</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4663</t>
+          <t>0; 5374</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2481</t>
+          <t>0; 2562</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3619; 15552</t>
+          <t>3666; 14506</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2189; 17464</t>
+          <t>2792; 17667</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1825; 10836</t>
+          <t>1807; 11188</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1130; 8288</t>
+          <t>892; 8464</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24534; 49733</t>
+          <t>25161; 49639</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29005; 53669</t>
+          <t>28732; 55954</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22244; 45149</t>
+          <t>22188; 44999</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12321; 27723</t>
+          <t>12210; 28048</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3529; 16377</t>
+          <t>3470; 17009</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1001; 9173</t>
+          <t>997; 8400</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2923; 13416</t>
+          <t>2097; 12756</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3770; 19897</t>
+          <t>3531; 18543</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31280; 59731</t>
+          <t>31509; 57626</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31952; 58113</t>
+          <t>31445; 58423</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26884; 52659</t>
+          <t>26608; 52468</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18669; 38840</t>
+          <t>17705; 39486</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32C-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32C-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,95</t>
+          <t>1,37; 4,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,34</t>
+          <t>0,95; 3,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,16</t>
+          <t>2,05; 6,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,05</t>
+          <t>1,96; 6,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,6</t>
+          <t>0,0; 6,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,52</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,72</t>
+          <t>1,32; 3,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,41</t>
+          <t>0,6; 2,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,99</t>
+          <t>1,72; 5,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,99</t>
+          <t>1,74; 5,1</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,8</t>
+          <t>0,96; 2,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,83</t>
+          <t>1,32; 2,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,95</t>
+          <t>0,67; 1,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,36</t>
+          <t>0,29; 1,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,88</t>
+          <t>0,19; 1,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,36</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,48</t>
+          <t>0,15; 1,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,49</t>
+          <t>0,8; 3,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,97</t>
+          <t>0,83; 2,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,11</t>
+          <t>0,97; 2,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,52</t>
+          <t>0,59; 1,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,47</t>
+          <t>0,62; 1,85</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,97</t>
+          <t>0,78; 4,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,37</t>
+          <t>0,88; 5,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,63</t>
+          <t>0,27; 2,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,21</t>
+          <t>0,41; 2,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,66</t>
+          <t>0,63; 2,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,23</t>
+          <t>0,39; 3,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,71</t>
+          <t>0,28; 1,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,43</t>
+          <t>0,22; 1,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1137,32 +1137,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,64</t>
+          <t>1,3; 2,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,76</t>
+          <t>1,4; 2,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,28</t>
+          <t>1,08; 2,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,78</t>
+          <t>0,71; 1,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,9</t>
+          <t>0,41; 1,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,81</t>
+          <t>0,1; 0,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,81</t>
+          <t>0,58; 2,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,08</t>
+          <t>1,13; 2,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,9</t>
+          <t>1,04; 1,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,69</t>
+          <t>0,86; 1,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,52</t>
+          <t>0,87; 1,74</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>888</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>10105</t>
         </is>
       </c>
     </row>
@@ -1504,27 +1504,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6571; 18582</t>
+          <t>6460; 19208</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4596; 16885</t>
+          <t>4805; 18189</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7105; 21665</t>
+          <t>7196; 22707</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4442; 14753</t>
+          <t>5064; 15714</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 11058</t>
+          <t>0; 10831</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1534,32 +1534,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6176</t>
+          <t>0; 5821</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2935</t>
+          <t>0; 3079</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8438; 23738</t>
+          <t>8424; 24487</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4754; 17646</t>
+          <t>4410; 16597</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8246; 24350</t>
+          <t>8372; 25489</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5432; 15523</t>
+          <t>5813; 16990</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14709</t>
+          <t>17206</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10449; 29667</t>
+          <t>10128; 27454</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15246; 33909</t>
+          <t>15770; 34220</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8534; 24197</t>
+          <t>8377; 23941</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3033; 13363</t>
+          <t>3072; 13036</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1016; 10035</t>
+          <t>1018; 10076</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>991; 8031</t>
+          <t>0; 8109</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1087; 10525</t>
+          <t>1088; 9532</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2242; 17662</t>
+          <t>4502; 21319</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12883; 31376</t>
+          <t>13226; 31749</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17997; 37744</t>
+          <t>17439; 37442</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11700; 29816</t>
+          <t>11571; 29734</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7624; 24961</t>
+          <t>10011; 29644</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>548</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>4191</t>
         </is>
       </c>
     </row>
@@ -1920,27 +1920,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2846; 13913</t>
+          <t>2732; 14062</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2800; 17399</t>
+          <t>2838; 17295</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1055; 9874</t>
+          <t>1032; 9564</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>746; 7611</t>
+          <t>1519; 9759</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5512</t>
+          <t>0; 5727</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1950,32 +1950,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5374</t>
+          <t>0; 4995</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2562</t>
+          <t>0; 3050</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3666; 14506</t>
+          <t>3419; 15195</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2792; 17667</t>
+          <t>2158; 18029</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1807; 11188</t>
+          <t>1803; 10223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>892; 8464</t>
+          <t>1434; 9706</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>31502</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25161; 49639</t>
+          <t>24416; 48743</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28732; 55954</t>
+          <t>28473; 54336</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22188; 44999</t>
+          <t>21335; 45455</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12210; 28048</t>
+          <t>11814; 28175</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3470; 17009</t>
+          <t>3702; 16168</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>997; 8400</t>
+          <t>992; 8150</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2097; 12756</t>
+          <t>2101; 12749</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3531; 18543</t>
+          <t>5215; 22810</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31509; 57626</t>
+          <t>31482; 57897</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31445; 58423</t>
+          <t>31776; 58196</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26608; 52468</t>
+          <t>26779; 51856</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17705; 39486</t>
+          <t>22496; 44735</t>
         </is>
       </c>
     </row>
